--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED05.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED05.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:52+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>180W</t>
+          <t>134W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -1617,7 +1617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L4"/>
+  <dimension ref="B2:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -1700,7 +1700,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-3-0022</t>
+          <t>SIM_XA_FIXED-2-0080</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40W</t>
+          <t>29W</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>第3年</t>
+          <t>第2年</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0季</t>
+          <t>3季</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1748,7 +1748,62 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年3季</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SIM_XA_FIXED-4-0037</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>本地</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>121W</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>已交</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>第4年</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5季</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1季</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>第4年4季</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G50"/>
+  <dimension ref="B2:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2086,10 +2141,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="E14" t="n">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2098,7 +2153,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2170,7 @@
         <v>-14</v>
       </c>
       <c r="E15" t="n">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2141,7 +2196,7 @@
         <v>-10</v>
       </c>
       <c r="E16" t="n">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2167,7 +2222,7 @@
         <v>-14</v>
       </c>
       <c r="E17" t="n">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2193,7 +2248,7 @@
         <v>-14</v>
       </c>
       <c r="E18" t="n">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2219,7 +2274,7 @@
         <v>-14</v>
       </c>
       <c r="E19" t="n">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2245,7 +2300,7 @@
         <v>-15</v>
       </c>
       <c r="E20" t="n">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2271,7 +2326,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2297,7 +2352,7 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2316,14 +2371,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="E23" t="n">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2332,7 +2387,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
         </is>
       </c>
     </row>
@@ -2342,14 +2397,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="E24" t="n">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2358,7 +2413,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-dca086d6d6", "line_id": "L-6f8d221dce", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2368,23 +2423,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-12</v>
       </c>
       <c r="E25" t="n">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2394,23 +2449,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="E26" t="n">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-37ad199110", "line_id": "L-6f8d221dce", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2482,7 @@
         <v>-14</v>
       </c>
       <c r="E27" t="n">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2446,14 +2501,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2462,7 +2517,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-2-0080", "receivable_term_quarters": 3, "revenue_wan": 29.0}</t>
         </is>
       </c>
     </row>
@@ -2472,23 +2527,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>40</v>
+        <v>-12</v>
       </c>
       <c r="E29" t="n">
-        <v>373</v>
+        <v>327</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-3-0022", "receivable_term_quarters": 0, "revenue_wan": 40.0}</t>
+          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
         </is>
       </c>
     </row>
@@ -2498,23 +2553,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="E30" t="n">
-        <v>361</v>
+        <v>319</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-917b7802bb", "line_id": "L-6f8d221dce", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2524,23 +2579,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-9cd40f73fd", "line_id": "L-6f8d221dce", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2612,7 @@
         <v>-14</v>
       </c>
       <c r="E32" t="n">
-        <v>339</v>
+        <v>291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2583,7 +2638,7 @@
         <v>-15</v>
       </c>
       <c r="E33" t="n">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2609,7 +2664,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2635,7 +2690,7 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2658,10 +2713,10 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="E36" t="n">
-        <v>316</v>
+        <v>264</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2670,7 +2725,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2742,7 @@
         <v>-14</v>
       </c>
       <c r="E37" t="n">
-        <v>302</v>
+        <v>250</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2706,23 +2761,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-14</v>
+        <v>29</v>
       </c>
       <c r="E38" t="n">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>receivable_collected | {"receivable_id": "AR-d54b285dd6"}</t>
         </is>
       </c>
     </row>
@@ -2732,23 +2787,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-14</v>
+        <v>-36</v>
       </c>
       <c r="E39" t="n">
-        <v>274</v>
+        <v>243</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>emergency_material_purchase | {"cost_wan": 36.0, "material_id": "R1", "quantity": 3.0}</t>
         </is>
       </c>
     </row>
@@ -2758,23 +2813,23 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-14</v>
+        <v>-24</v>
       </c>
       <c r="E40" t="n">
-        <v>260</v>
+        <v>219</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 60.0, "job_id": "JOB-8cd522af83", "line_id": "L-6f8d221dce", "product_id": "P1", "quantity": 3.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2784,23 +2839,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E41" t="n">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-6f8d221dce"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2810,23 +2865,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E42" t="n">
-        <v>245</v>
+        <v>191</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-6f8d221dce", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2836,14 +2891,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>245</v>
+        <v>191</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2852,7 +2907,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-6f8d221dce", "asset_type": "production_line"}</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-4-0037", "receivable_term_quarters": 1, "revenue_wan": 121.0}</t>
         </is>
       </c>
     </row>
@@ -2862,23 +2917,23 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-8</v>
+        <v>-48</v>
       </c>
       <c r="E44" t="n">
-        <v>237</v>
+        <v>143</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
         </is>
       </c>
     </row>
@@ -2888,23 +2943,23 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-14</v>
+        <v>-32</v>
       </c>
       <c r="E45" t="n">
-        <v>223</v>
+        <v>111</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-156517a22e", "line_id": "L-6f8d221dce", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2921,11 +2976,11 @@
         <v>-14</v>
       </c>
       <c r="E46" t="n">
-        <v>209</v>
+        <v>97</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>第5年2季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2940,23 +2995,23 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-14</v>
+        <v>121</v>
       </c>
       <c r="E47" t="n">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>第5年3季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>receivable_collected | {"receivable_id": "AR-899c1e392a"}</t>
         </is>
       </c>
     </row>
@@ -2973,11 +3028,11 @@
         <v>-15</v>
       </c>
       <c r="E48" t="n">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>第5年4季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2999,11 +3054,11 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>第5年4季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3025,14 +3080,196 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
+          <t>第4年4季</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-6f8d221dce", "asset_type": "production_line"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>48</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Pay_AD</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>-12</v>
+      </c>
+      <c r="E51" t="n">
+        <v>191</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>第5年1季</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>49</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Pay_Overhaul</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>-14</v>
+      </c>
+      <c r="E52" t="n">
+        <v>177</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>第5年1季</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>management_fee_expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>50</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Pay_Overhaul</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>-14</v>
+      </c>
+      <c r="E53" t="n">
+        <v>163</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>第5年2季</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>management_fee_expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>51</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Pay_Overhaul</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>-14</v>
+      </c>
+      <c r="E54" t="n">
+        <v>149</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>第5年3季</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>management_fee_expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>52</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Pay_Maintenance</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>-15</v>
+      </c>
+      <c r="E55" t="n">
+        <v>134</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>第5年4季</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>maintenance_expense | {"line_id": "L-6f8d221dce"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>53</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>134</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>第5年4季</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-6f8d221dce", "asset_type": "factory"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>54</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>134</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>第5年4季</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
         <is>
           <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-6f8d221dce", "asset_type": "production_line"}</t>
         </is>
@@ -3139,16 +3376,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -3364,16 +3601,16 @@
         <v>71</v>
       </c>
       <c r="E13" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F13" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G13" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H13" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -3429,10 +3666,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -3457,7 +3694,7 @@
         <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -3479,10 +3716,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -3501,16 +3738,16 @@
         <v>71</v>
       </c>
       <c r="E19" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F19" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G19" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H19" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
@@ -3526,16 +3763,16 @@
         <v>-71</v>
       </c>
       <c r="E20" t="n">
-        <v>-79</v>
+        <v>-83</v>
       </c>
       <c r="F20" t="n">
-        <v>-59</v>
+        <v>-74</v>
       </c>
       <c r="G20" t="n">
-        <v>-79</v>
+        <v>-42</v>
       </c>
       <c r="H20" t="n">
-        <v>-65</v>
+        <v>-69</v>
       </c>
     </row>
     <row r="21">
@@ -3576,16 +3813,16 @@
         <v>-86.2</v>
       </c>
       <c r="E22" t="n">
-        <v>-94.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-74.2</v>
+        <v>-89.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-94.2</v>
+        <v>-57.2</v>
       </c>
       <c r="H22" t="n">
-        <v>-80.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="23">
@@ -3626,16 +3863,16 @@
         <v>-86.2</v>
       </c>
       <c r="E24" t="n">
-        <v>-104.2</v>
+        <v>-108.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-74.2</v>
+        <v>-89.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-94.2</v>
+        <v>-57.2</v>
       </c>
       <c r="H24" t="n">
-        <v>-80.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="25">
@@ -3676,16 +3913,16 @@
         <v>-86.2</v>
       </c>
       <c r="E26" t="n">
-        <v>-104.2</v>
+        <v>-108.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-74.2</v>
+        <v>-89.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-94.2</v>
+        <v>-57.2</v>
       </c>
       <c r="H26" t="n">
-        <v>-80.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="28">
@@ -3775,16 +4012,16 @@
         <v>492</v>
       </c>
       <c r="E30" t="n">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="F30" t="n">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="G30" t="n">
-        <v>245</v>
+        <v>203</v>
       </c>
       <c r="H30" t="n">
-        <v>180</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31">
@@ -3803,7 +4040,7 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -3828,10 +4065,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3853,13 +4090,13 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G33" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34">
@@ -3900,16 +4137,16 @@
         <v>492</v>
       </c>
       <c r="E35" t="n">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="F35" t="n">
-        <v>344</v>
+        <v>325</v>
       </c>
       <c r="G35" t="n">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="H35" t="n">
-        <v>200</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36">
@@ -4025,16 +4262,16 @@
         <v>588.8</v>
       </c>
       <c r="E40" t="n">
-        <v>484.6</v>
+        <v>480.6</v>
       </c>
       <c r="F40" t="n">
-        <v>410.4</v>
+        <v>391.4</v>
       </c>
       <c r="G40" t="n">
-        <v>316.2</v>
+        <v>334.2</v>
       </c>
       <c r="H40" t="n">
-        <v>236</v>
+        <v>250</v>
       </c>
     </row>
     <row r="41">
@@ -4203,13 +4440,13 @@
         <v>-86.20000000000003</v>
       </c>
       <c r="F47" t="n">
-        <v>-190.4</v>
+        <v>-194.4</v>
       </c>
       <c r="G47" t="n">
-        <v>-264.6</v>
+        <v>-283.6</v>
       </c>
       <c r="H47" t="n">
-        <v>-358.8</v>
+        <v>-340.8</v>
       </c>
     </row>
     <row r="48">
@@ -4225,16 +4462,16 @@
         <v>-86.2</v>
       </c>
       <c r="E48" t="n">
-        <v>-104.2</v>
+        <v>-108.2</v>
       </c>
       <c r="F48" t="n">
-        <v>-74.2</v>
+        <v>-89.2</v>
       </c>
       <c r="G48" t="n">
-        <v>-94.2</v>
+        <v>-57.2</v>
       </c>
       <c r="H48" t="n">
-        <v>-80.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="49">
@@ -4250,16 +4487,16 @@
         <v>588.8</v>
       </c>
       <c r="E49" t="n">
-        <v>484.6</v>
+        <v>480.6</v>
       </c>
       <c r="F49" t="n">
-        <v>410.4</v>
+        <v>391.4</v>
       </c>
       <c r="G49" t="n">
-        <v>316.2</v>
+        <v>334.2</v>
       </c>
       <c r="H49" t="n">
-        <v>236</v>
+        <v>250</v>
       </c>
     </row>
     <row r="50">
@@ -4275,16 +4512,16 @@
         <v>588.8</v>
       </c>
       <c r="E50" t="n">
-        <v>484.6</v>
+        <v>480.6</v>
       </c>
       <c r="F50" t="n">
-        <v>410.4</v>
+        <v>391.4</v>
       </c>
       <c r="G50" t="n">
-        <v>316.2</v>
+        <v>334.2</v>
       </c>
       <c r="H50" t="n">
-        <v>236</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -4355,7 +4592,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4504,7 +4741,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -4653,7 +4890,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -4802,7 +5039,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -4951,7 +5188,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
